--- a/gal/Assets/Resources/VNovelizerRes/ExcelVNScripts/第三章.xlsx
+++ b/gal/Assets/Resources/VNovelizerRes/ExcelVNScripts/第三章.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="101">
   <si>
     <t>ID</t>
   </si>
@@ -65,73 +65,76 @@
     <t>Note</t>
   </si>
   <si>
+    <t>hide</t>
+  </si>
+  <si>
+    <t>外面在下雨...</t>
+  </si>
+  <si>
+    <t>病房</t>
+  </si>
+  <si>
+    <t>平静小曲</t>
+  </si>
+  <si>
+    <t>下雨粒子特效</t>
+  </si>
+  <si>
+    <t>淅沥淅沥......</t>
+  </si>
+  <si>
+    <t>悠然惬意的日子吗</t>
+  </si>
+  <si>
+    <t>工作了一年，好像很久没发过呆了</t>
+  </si>
+  <si>
+    <t>平淡日常中的意外也有让人惊喜的地方呢</t>
+  </si>
+  <si>
+    <t>害，如果能一直带薪休假就好了</t>
+  </si>
+  <si>
+    <t>我是不是好久都没看手机消息了</t>
+  </si>
+  <si>
+    <t>打开手机看一眼吧</t>
+  </si>
+  <si>
+    <t>同事</t>
+  </si>
+  <si>
+    <t>"你身体咋样了"</t>
+  </si>
+  <si>
+    <t>"好好休息"</t>
+  </si>
+  <si>
+    <t>"？还活着吗"</t>
+  </si>
+  <si>
+    <t>我靠，两天没回他消息了</t>
+  </si>
+  <si>
+    <t>"还活着，恢复得比想象中快，应该过几天就出院了"</t>
+  </si>
+  <si>
+    <t>放下手机</t>
+  </si>
+  <si>
+    <t>嘟~嘟~</t>
+  </si>
+  <si>
+    <t>居然打电话过来了</t>
+  </si>
+  <si>
+    <t>你在哪个医院，我有时间来看看你</t>
+  </si>
+  <si>
     <t>Me</t>
   </si>
   <si>
-    <t>hide</t>
-  </si>
-  <si>
-    <t>外面在下雨...</t>
-  </si>
-  <si>
-    <t>医院早</t>
-  </si>
-  <si>
-    <t>平静小曲</t>
-  </si>
-  <si>
-    <t>下雨粒子特效</t>
-  </si>
-  <si>
-    <t>淅沥淅沥......</t>
-  </si>
-  <si>
-    <t>病房</t>
-  </si>
-  <si>
-    <t>不得不说，真是惬意啊...</t>
-  </si>
-  <si>
-    <t>工作了一年，好像就没怎么有这样什么也不用干什么也不用想的时间</t>
-  </si>
-  <si>
-    <t>这次住院是一个短暂的意外</t>
-  </si>
-  <si>
-    <t>害，如果能一直带薪休假就好了</t>
-  </si>
-  <si>
-    <t>（有点忘记看手机了）</t>
-  </si>
-  <si>
-    <t>同事</t>
-  </si>
-  <si>
-    <t>你身体咋样了</t>
-  </si>
-  <si>
-    <t>好好休息</t>
-  </si>
-  <si>
-    <t>？你还活着吗</t>
-  </si>
-  <si>
-    <t>（我靠，我两天没回复他了）</t>
-  </si>
-  <si>
-    <t>还活着，好得快，应该出院也不会慢</t>
-  </si>
-  <si>
-    <t>（放下手机）</t>
-  </si>
-  <si>
-    <t>嘟~嘟~</t>
-  </si>
-  <si>
-    <t>你在哪个医院，我有时间来看看你</t>
-  </si>
-  <si>
-    <t>**人民医院，探望不用带东西</t>
+    <t>人民医院，探望不用带东西</t>
   </si>
   <si>
     <t>额，你还是带点零食来吧</t>
@@ -140,7 +143,7 @@
     <t>你真的虚到两天看不了手机吗</t>
   </si>
   <si>
-    <t>私密马赛，我戳了</t>
+    <t>私密马赛，我错了</t>
   </si>
   <si>
     <t>行吧，我明天下班再来，你保重</t>
@@ -149,10 +152,10 @@
     <t>......</t>
   </si>
   <si>
-    <t>哦呀，原来还是有人在意我的（馆长笑）</t>
-  </si>
-  <si>
-    <t>外面还在下雨...</t>
+    <t>原来还是有人在意我的，谢谢你，同事哥</t>
+  </si>
+  <si>
+    <t>外面的雨还在下，这季节...</t>
   </si>
   <si>
     <t>按下按钮......</t>
@@ -173,13 +176,146 @@
     <t>那聊一会小妍吧</t>
   </si>
   <si>
-    <t>......好的</t>
+    <t>护士不能透露病患信息哦</t>
   </si>
   <si>
     <t>医院里的小孩不多吧，平常会有人陪她玩吗</t>
   </si>
   <si>
-    <t>小妍的话情况比较特殊，她是长时间住院的小朋友，一般住院的其他小朋友会玩到一起，然后陆续出院，但小妍现在得一直待在这里</t>
+    <t>不能透露哦</t>
+  </si>
+  <si>
+    <t>hidesuwa</t>
+  </si>
+  <si>
+    <t>ciallo~</t>
+  </si>
+  <si>
+    <t>油盐不进啊，毕竟这也是她的职责</t>
+  </si>
+  <si>
+    <t>晚上我看看剧本，监修一下</t>
+  </si>
+  <si>
+    <t>为什么她能吃我给的糖了？</t>
+  </si>
+  <si>
+    <t>说实话，有点生硬的说</t>
+  </si>
+  <si>
+    <t>嗯~为什么呢~</t>
+  </si>
+  <si>
+    <t>但还是好糖</t>
+  </si>
+  <si>
+    <t>可能是因为神的旨意吧~</t>
+  </si>
+  <si>
+    <t>虽然好点了</t>
+  </si>
+  <si>
+    <t>那个猎奇神明不会给她催眠了吧...想象不出下达旨意的场景啊</t>
+  </si>
+  <si>
+    <t>怎么还有同事</t>
+  </si>
+  <si>
+    <t>我说图片资源，因为一直在找一直在更新</t>
+  </si>
+  <si>
+    <t>好糖</t>
+  </si>
+  <si>
+    <t>那我不打扰你了，工作加油~</t>
+  </si>
+  <si>
+    <t>文件夹拉到哪</t>
+  </si>
+  <si>
+    <t>你写就行了，文件我会导入游戏</t>
+  </si>
+  <si>
+    <t>悄悄去看看小妍...</t>
+  </si>
+  <si>
+    <t>走廊</t>
+  </si>
+  <si>
+    <t>反正这游戏不是大众类型</t>
+  </si>
+  <si>
+    <t>敲门</t>
+  </si>
+  <si>
+    <t>小妍</t>
+  </si>
+  <si>
+    <t>小妍_normal</t>
+  </si>
+  <si>
+    <t>护士姐姐？</t>
+  </si>
+  <si>
+    <t>咦嘻嘻，是哥哥我口牙</t>
+  </si>
+  <si>
+    <t>小妍_doubt</t>
+  </si>
+  <si>
+    <t>Oioioi，你那是什么表情</t>
+  </si>
+  <si>
+    <t>小妍_smile</t>
+  </si>
+  <si>
+    <t>原来会有这么不严肃的大人~</t>
+  </si>
+  <si>
+    <t>真是被看扁了啊...</t>
+  </si>
+  <si>
+    <t>小妍_angry</t>
+  </si>
+  <si>
+    <t>盯~</t>
+  </si>
+  <si>
+    <t>你盯着我干嘛</t>
+  </si>
+  <si>
+    <t>不知道</t>
+  </si>
+  <si>
+    <t>小妍_worry</t>
+  </si>
+  <si>
+    <t>叔叔你不会是没朋友吧...</t>
+  </si>
+  <si>
+    <t>你怎么知...等等，我才没有到当叔叔的年龄啊！</t>
+  </si>
+  <si>
+    <t>真是没办法，我可以当你的朋友哦~</t>
+  </si>
+  <si>
+    <t>可恶，怎么被小孩耍得团团转</t>
+  </si>
+  <si>
+    <t>我才没有不想要你当我朋友呢</t>
+  </si>
+  <si>
+    <t>噗~</t>
+  </si>
+  <si>
+    <t>可恶啊，这样下去我不会变得不想出院了吧</t>
+  </si>
+  <si>
+    <t>choice(进入第四章|loadScript(第四章,1000))</t>
+  </si>
+  <si>
+    <t>小妍的话情况比较特殊，她是长时间住院的小朋友，一般住院的其他
+小朋友会玩到一起，然后陆续出院，但小妍现在得一直待在这里</t>
   </si>
   <si>
     <t>这孩子本来也不爱说话，平常就没见到她跟其他小朋友待在一块呢~</t>
@@ -188,139 +324,13 @@
     <t>你是说她看起来是孤独的</t>
   </si>
   <si>
-    <t>hidesuwa</t>
-  </si>
-  <si>
-    <t>ciallo~</t>
-  </si>
-  <si>
     <t>我平常也有在特殊关照小妍，但是这孩子反而更亲我，不愿意交朋友了</t>
   </si>
   <si>
-    <t>晚上我看看剧本，监修一下</t>
-  </si>
-  <si>
     <t>她喜欢吃甜食，但是被管制得很严格</t>
   </si>
   <si>
-    <t>说实话，有点生硬的说</t>
-  </si>
-  <si>
     <t>是这样的</t>
-  </si>
-  <si>
-    <t>但还是好糖</t>
-  </si>
-  <si>
-    <t>那为啥又允许她吃我给的糖了</t>
-  </si>
-  <si>
-    <t>虽然好点了</t>
-  </si>
-  <si>
-    <t>嗯~为什么呢~</t>
-  </si>
-  <si>
-    <t>怎么还有同事</t>
-  </si>
-  <si>
-    <t>我说图片资源，因为一直在找一直在更新</t>
-  </si>
-  <si>
-    <t>可能是因为神的旨意吧~</t>
-  </si>
-  <si>
-    <t>好糖</t>
-  </si>
-  <si>
-    <t>（那个猎奇神明不会给她催眠了吧...想象不出下达旨意的场景啊）</t>
-  </si>
-  <si>
-    <t>文件夹拉到哪</t>
-  </si>
-  <si>
-    <t>你写就行了，文件我会导入游戏</t>
-  </si>
-  <si>
-    <t>反正这游戏不是大众类型</t>
-  </si>
-  <si>
-    <t>那我不打扰你了，工作加油~</t>
-  </si>
-  <si>
-    <t>悄悄去看看小妍...</t>
-  </si>
-  <si>
-    <t>走廊</t>
-  </si>
-  <si>
-    <t>（扣扣扣）</t>
-  </si>
-  <si>
-    <t>小妍</t>
-  </si>
-  <si>
-    <t>小妍_normal</t>
-  </si>
-  <si>
-    <t>护士姐姐？</t>
-  </si>
-  <si>
-    <t>咦嘻嘻，是哥哥我口牙</t>
-  </si>
-  <si>
-    <t>小妍_doubt</t>
-  </si>
-  <si>
-    <t>Oioioi，你那是什么表情</t>
-  </si>
-  <si>
-    <t>小妍_smile</t>
-  </si>
-  <si>
-    <t>原来会有这么不严肃的大人~</t>
-  </si>
-  <si>
-    <t>真是被看扁了啊...</t>
-  </si>
-  <si>
-    <t>小妍_angry</t>
-  </si>
-  <si>
-    <t>（盯~）</t>
-  </si>
-  <si>
-    <t>你盯着我干嘛</t>
-  </si>
-  <si>
-    <t>不知道</t>
-  </si>
-  <si>
-    <t>小妍_worry</t>
-  </si>
-  <si>
-    <t>叔叔你不会是没朋友吧...</t>
-  </si>
-  <si>
-    <t>你怎么知...等等，我才没有到当叔叔的年龄啊！</t>
-  </si>
-  <si>
-    <t>真是没办法，我可以当你的朋友哦~</t>
-  </si>
-  <si>
-    <t>（可恶，怎么被小孩耍得团团转）</t>
-  </si>
-  <si>
-    <t>我才没有不想要你当我朋友呢</t>
-  </si>
-  <si>
-    <t>噗~</t>
-  </si>
-  <si>
-    <t>（真是不得了的忘年交...可恶啊，这样下去我不会变得不想出院了吧）</t>
-  </si>
-  <si>
-    <t>跳转第四章</t>
   </si>
 </sst>
 </file>
@@ -941,7 +951,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -949,6 +959,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1269,7 +1282,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q64"/>
+  <dimension ref="A1:Q95"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="3" max="3" width="14.6" customWidth="1"/>
@@ -1332,30 +1345,30 @@
         <v>12</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G2" s="2" t="s">
+      <c r="H2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="I2" s="2" t="s">
         <v>15</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>16</v>
       </c>
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
       <c r="L2" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M2" s="2"/>
       <c r="N2" s="2"/>
@@ -1375,11 +1388,9 @@
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
       <c r="G3" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>19</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="H3" s="2"/>
       <c r="I3" s="2"/>
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
@@ -1402,7 +1413,7 @@
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
       <c r="G4" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
@@ -1427,7 +1438,7 @@
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H5" s="2"/>
       <c r="I5" s="2"/>
@@ -1452,7 +1463,7 @@
       <c r="E6" s="2"/>
       <c r="F6" s="2"/>
       <c r="G6" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
@@ -1477,7 +1488,7 @@
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
       <c r="G7" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
@@ -1502,7 +1513,7 @@
       <c r="E8" s="2"/>
       <c r="F8" s="2"/>
       <c r="G8" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
@@ -1519,21 +1530,12 @@
       <c r="A9" s="2">
         <v>1007</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2"/>
-      <c r="K9" s="2"/>
-      <c r="L9" s="2"/>
+      <c r="B9" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9" t="s">
+        <v>23</v>
+      </c>
       <c r="M9" s="2"/>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1545,14 +1547,14 @@
         <v>1008</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
       <c r="G10" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H10" s="2"/>
       <c r="I10" s="2"/>
@@ -1570,14 +1572,14 @@
         <v>1009</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
       <c r="G11" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H11" s="2"/>
       <c r="I11" s="2"/>
@@ -1595,14 +1597,14 @@
         <v>1010</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
       <c r="G12" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
@@ -1627,7 +1629,7 @@
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
       <c r="G13" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H13" s="2"/>
       <c r="I13" s="2"/>
@@ -1652,7 +1654,7 @@
       <c r="E14" s="2"/>
       <c r="F14" s="2"/>
       <c r="G14" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="H14" s="2"/>
       <c r="I14" s="2"/>
@@ -1670,14 +1672,14 @@
         <v>1013</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
       <c r="G15" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H15" s="2"/>
       <c r="I15" s="2"/>
@@ -1695,14 +1697,14 @@
         <v>1014</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
       <c r="F16" s="2"/>
       <c r="G16" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H16" s="2"/>
       <c r="I16" s="2"/>
@@ -1719,21 +1721,12 @@
       <c r="A17" s="2">
         <v>1015</v>
       </c>
-      <c r="B17" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="H17" s="2"/>
-      <c r="I17" s="2"/>
-      <c r="J17" s="2"/>
-      <c r="K17" s="2"/>
-      <c r="L17" s="2"/>
+      <c r="B17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G17" t="s">
+        <v>32</v>
+      </c>
       <c r="M17" s="2"/>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -1745,14 +1738,14 @@
         <v>1016</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
       <c r="E18" s="2"/>
       <c r="F18" s="2"/>
       <c r="G18" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
@@ -1770,14 +1763,14 @@
         <v>1017</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" s="2"/>
       <c r="E19" s="2"/>
       <c r="F19" s="2"/>
       <c r="G19" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H19" s="2"/>
       <c r="I19" s="2"/>
@@ -1795,14 +1788,14 @@
         <v>1018</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
       <c r="E20" s="2"/>
       <c r="F20" s="2"/>
       <c r="G20" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H20" s="2"/>
       <c r="I20" s="2"/>
@@ -1820,14 +1813,14 @@
         <v>1019</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" s="2"/>
       <c r="E21" s="2"/>
       <c r="F21" s="2"/>
       <c r="G21" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H21" s="2"/>
       <c r="I21" s="2"/>
@@ -1845,14 +1838,14 @@
         <v>1020</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
       <c r="E22" s="2"/>
       <c r="F22" s="2"/>
       <c r="G22" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H22" s="2"/>
       <c r="I22" s="2"/>
@@ -1870,14 +1863,14 @@
         <v>1021</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" s="2"/>
       <c r="E23" s="2"/>
       <c r="F23" s="2"/>
       <c r="G23" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H23" s="2"/>
       <c r="I23" s="2"/>
@@ -1902,7 +1895,7 @@
       <c r="E24" s="2"/>
       <c r="F24" s="2"/>
       <c r="G24" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H24" s="2"/>
       <c r="I24" s="2"/>
@@ -1927,7 +1920,7 @@
       <c r="E25" s="2"/>
       <c r="F25" s="2"/>
       <c r="G25" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H25" s="2"/>
       <c r="I25" s="2"/>
@@ -1945,14 +1938,14 @@
         <v>1024</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>43</v>
+        <v>12</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" s="2"/>
       <c r="E26" s="2"/>
       <c r="F26" s="2"/>
       <c r="G26" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H26" s="2"/>
       <c r="I26" s="2"/>
@@ -1977,7 +1970,7 @@
       <c r="E27" s="2"/>
       <c r="F27" s="2"/>
       <c r="G27" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="H27" s="2"/>
       <c r="I27" s="2"/>
@@ -1995,14 +1988,14 @@
         <v>1026</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" s="2"/>
       <c r="E28" s="2"/>
       <c r="F28" s="2"/>
       <c r="G28" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H28" s="2"/>
       <c r="I28" s="2"/>
@@ -2020,14 +2013,14 @@
         <v>1027</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" s="2"/>
       <c r="E29" s="2"/>
       <c r="F29" s="2"/>
       <c r="G29" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H29" s="2"/>
       <c r="I29" s="2"/>
@@ -2045,14 +2038,14 @@
         <v>1028</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" s="2"/>
       <c r="E30" s="2"/>
       <c r="F30" s="2"/>
       <c r="G30" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H30" s="2"/>
       <c r="I30" s="2"/>
@@ -2070,14 +2063,14 @@
         <v>1029</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" s="2"/>
       <c r="E31" s="2"/>
       <c r="F31" s="2"/>
       <c r="G31" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H31" s="2"/>
       <c r="I31" s="2"/>
@@ -2095,14 +2088,14 @@
         <v>1030</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" s="2"/>
       <c r="E32" s="2"/>
       <c r="F32" s="2"/>
       <c r="G32" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H32" s="2"/>
       <c r="I32" s="2"/>
@@ -2120,14 +2113,14 @@
         <v>1031</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" s="2"/>
       <c r="E33" s="2"/>
       <c r="F33" s="2"/>
       <c r="G33" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H33" s="2"/>
       <c r="I33" s="2"/>
@@ -2145,14 +2138,14 @@
         <v>1032</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>12</v>
+        <v>44</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" s="2"/>
       <c r="E34" s="2"/>
       <c r="F34" s="2"/>
-      <c r="G34" s="2" t="s">
-        <v>52</v>
+      <c r="G34" t="s">
+        <v>51</v>
       </c>
       <c r="H34" s="2"/>
       <c r="I34" s="2"/>
@@ -2161,10 +2154,10 @@
       <c r="L34" s="2"/>
       <c r="M34" s="2"/>
       <c r="N34" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="O34" s="2" t="s">
         <v>53</v>
-      </c>
-      <c r="O34" s="2" t="s">
-        <v>54</v>
       </c>
       <c r="P34" s="2"/>
       <c r="Q34" s="2"/>
@@ -2174,14 +2167,14 @@
         <v>1033</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>43</v>
+        <v>12</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" s="2"/>
       <c r="E35" s="2"/>
       <c r="F35" s="2"/>
-      <c r="G35" s="2" t="s">
-        <v>55</v>
+      <c r="G35" t="s">
+        <v>54</v>
       </c>
       <c r="H35" s="2"/>
       <c r="I35" s="2"/>
@@ -2189,7 +2182,7 @@
       <c r="K35" s="2"/>
       <c r="L35" s="2"/>
       <c r="M35" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="N35" s="3"/>
       <c r="O35" s="3"/>
@@ -2201,14 +2194,14 @@
         <v>1034</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" s="2"/>
       <c r="E36" s="2"/>
       <c r="F36" s="2"/>
       <c r="G36" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H36" s="2"/>
       <c r="I36" s="2"/>
@@ -2216,7 +2209,7 @@
       <c r="K36" s="2"/>
       <c r="L36" s="2"/>
       <c r="M36" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -2228,14 +2221,14 @@
         <v>1035</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" s="2"/>
       <c r="E37" s="2"/>
       <c r="F37" s="2"/>
       <c r="G37" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H37" s="2"/>
       <c r="I37" s="2"/>
@@ -2243,7 +2236,7 @@
       <c r="K37" s="2"/>
       <c r="L37" s="2"/>
       <c r="M37" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -2255,14 +2248,14 @@
         <v>1036</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>12</v>
+        <v>44</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" s="2"/>
       <c r="E38" s="2"/>
       <c r="F38" s="2"/>
       <c r="G38" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H38" s="2"/>
       <c r="I38" s="2"/>
@@ -2270,7 +2263,7 @@
       <c r="K38" s="2"/>
       <c r="L38" s="2"/>
       <c r="M38" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -2282,14 +2275,14 @@
         <v>1037</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>43</v>
+        <v>12</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" s="2"/>
       <c r="E39" s="2"/>
       <c r="F39" s="2"/>
       <c r="G39" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H39" s="2"/>
       <c r="I39" s="2"/>
@@ -2297,11 +2290,11 @@
       <c r="K39" s="2"/>
       <c r="L39" s="2"/>
       <c r="M39" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="P39" s="2"/>
       <c r="Q39" s="2"/>
@@ -2311,14 +2304,14 @@
         <v>1038</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" s="2"/>
       <c r="E40" s="2"/>
       <c r="F40" s="2"/>
       <c r="G40" s="2" t="s">
-        <v>66</v>
+        <v>40</v>
       </c>
       <c r="H40" s="2"/>
       <c r="I40" s="2"/>
@@ -2326,7 +2319,7 @@
       <c r="K40" s="2"/>
       <c r="L40" s="2"/>
       <c r="M40" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -2338,14 +2331,14 @@
         <v>1039</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" s="2"/>
       <c r="E41" s="2"/>
       <c r="F41" s="2"/>
       <c r="G41" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="H41" s="2"/>
       <c r="I41" s="2"/>
@@ -2353,11 +2346,11 @@
       <c r="K41" s="2"/>
       <c r="L41" s="2"/>
       <c r="M41" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="P41" s="3"/>
       <c r="Q41" s="3"/>
@@ -2367,16 +2360,18 @@
         <v>1040</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>43</v>
+        <v>12</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" s="2"/>
       <c r="E42" s="2"/>
       <c r="F42" s="2"/>
       <c r="G42" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="H42" s="2"/>
+        <v>69</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>70</v>
+      </c>
       <c r="I42" s="2"/>
       <c r="J42" s="2"/>
       <c r="K42" s="2"/>
@@ -2418,23 +2413,12 @@
       <c r="A44" s="2">
         <v>1042</v>
       </c>
-      <c r="B44" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C44" s="2"/>
-      <c r="D44" s="2"/>
-      <c r="E44" s="2"/>
-      <c r="F44" s="2"/>
-      <c r="G44" s="2" t="s">
-        <v>73</v>
+      <c r="B44" t="s">
+        <v>12</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="I44" s="2"/>
-      <c r="J44" s="2"/>
-      <c r="K44" s="2"/>
-      <c r="L44" s="2"/>
+        <v>14</v>
+      </c>
       <c r="M44" s="2"/>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -2446,18 +2430,18 @@
         <v>1043</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>12</v>
+        <v>73</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" s="2"/>
-      <c r="E45" s="2"/>
+      <c r="E45" s="2" t="s">
+        <v>74</v>
+      </c>
       <c r="F45" s="2"/>
       <c r="G45" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="H45" s="2" t="s">
-        <v>19</v>
-      </c>
+      <c r="H45" s="2"/>
       <c r="I45" s="2"/>
       <c r="J45" s="2"/>
       <c r="K45" s="2"/>
@@ -2473,16 +2457,16 @@
         <v>1044</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>76</v>
+        <v>34</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" s="2"/>
       <c r="E46" s="2" t="s">
-        <v>77</v>
+        <v>12</v>
       </c>
       <c r="F46" s="2"/>
       <c r="G46" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="H46" s="2"/>
       <c r="I46" s="2"/>
@@ -2500,16 +2484,16 @@
         <v>1045</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>12</v>
+        <v>73</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" s="2"/>
       <c r="E47" s="2" t="s">
-        <v>13</v>
+        <v>77</v>
       </c>
       <c r="F47" s="2"/>
       <c r="G47" s="2" t="s">
-        <v>79</v>
+        <v>40</v>
       </c>
       <c r="H47" s="2"/>
       <c r="I47" s="2"/>
@@ -2527,16 +2511,16 @@
         <v>1046</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>76</v>
+        <v>34</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" s="2"/>
       <c r="E48" s="2" t="s">
-        <v>80</v>
+        <v>12</v>
       </c>
       <c r="F48" s="2"/>
       <c r="G48" s="2" t="s">
-        <v>39</v>
+        <v>78</v>
       </c>
       <c r="H48" s="2"/>
       <c r="I48" s="2"/>
@@ -2554,16 +2538,16 @@
         <v>1047</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>12</v>
+        <v>73</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" s="2"/>
       <c r="E49" s="2" t="s">
-        <v>13</v>
+        <v>79</v>
       </c>
       <c r="F49" s="2"/>
       <c r="G49" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H49" s="2"/>
       <c r="I49" s="2"/>
@@ -2581,16 +2565,16 @@
         <v>1048</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>76</v>
+        <v>34</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" s="2"/>
       <c r="E50" s="2" t="s">
-        <v>82</v>
+        <v>12</v>
       </c>
       <c r="F50" s="2"/>
       <c r="G50" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="H50" s="2"/>
       <c r="I50" s="2"/>
@@ -2608,16 +2592,16 @@
         <v>1049</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>12</v>
+        <v>73</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" s="2"/>
       <c r="E51" s="2" t="s">
-        <v>13</v>
+        <v>74</v>
       </c>
       <c r="F51" s="2"/>
       <c r="G51" s="2" t="s">
-        <v>84</v>
+        <v>40</v>
       </c>
       <c r="H51" s="2"/>
       <c r="I51" s="2"/>
@@ -2635,16 +2619,16 @@
         <v>1050</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>76</v>
+        <v>34</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" s="2"/>
       <c r="E52" s="2" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="F52" s="2"/>
       <c r="G52" s="2" t="s">
-        <v>39</v>
+        <v>83</v>
       </c>
       <c r="H52" s="2"/>
       <c r="I52" s="2"/>
@@ -2662,16 +2646,16 @@
         <v>1051</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>12</v>
+        <v>73</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" s="2"/>
       <c r="E53" s="2" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="F53" s="2"/>
       <c r="G53" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H53" s="2"/>
       <c r="I53" s="2"/>
@@ -2689,14 +2673,14 @@
         <v>1052</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>76</v>
+        <v>34</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" s="2"/>
       <c r="E54" s="2"/>
       <c r="F54" s="2"/>
       <c r="G54" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H54" s="2"/>
       <c r="I54" s="2"/>
@@ -2714,16 +2698,16 @@
         <v>1053</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>12</v>
+        <v>73</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" s="2"/>
       <c r="E55" s="2" t="s">
-        <v>13</v>
+        <v>77</v>
       </c>
       <c r="F55" s="2"/>
       <c r="G55" s="2" t="s">
-        <v>88</v>
+        <v>40</v>
       </c>
       <c r="H55" s="2"/>
       <c r="I55" s="2"/>
@@ -2741,16 +2725,16 @@
         <v>1054</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" s="2"/>
       <c r="E56" s="2" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="F56" s="2"/>
       <c r="G56" s="2" t="s">
-        <v>39</v>
+        <v>87</v>
       </c>
       <c r="H56" s="2"/>
       <c r="I56" s="2"/>
@@ -2768,16 +2752,16 @@
         <v>1055</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>76</v>
+        <v>34</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" s="2"/>
       <c r="E57" s="2" t="s">
-        <v>89</v>
+        <v>12</v>
       </c>
       <c r="F57" s="2"/>
       <c r="G57" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H57" s="2"/>
       <c r="I57" s="2"/>
@@ -2795,16 +2779,16 @@
         <v>1056</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>12</v>
+        <v>73</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" s="2"/>
       <c r="E58" s="2" t="s">
-        <v>13</v>
+        <v>79</v>
       </c>
       <c r="F58" s="2"/>
       <c r="G58" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="H58" s="2"/>
       <c r="I58" s="2"/>
@@ -2822,16 +2806,16 @@
         <v>1057</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>76</v>
+        <v>12</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" s="2"/>
       <c r="E59" s="2" t="s">
-        <v>82</v>
+        <v>12</v>
       </c>
       <c r="F59" s="2"/>
       <c r="G59" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H59" s="2"/>
       <c r="I59" s="2"/>
@@ -2849,16 +2833,14 @@
         <v>1058</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" s="2"/>
-      <c r="E60" s="2" t="s">
-        <v>13</v>
-      </c>
+      <c r="E60" s="2"/>
       <c r="F60" s="2"/>
       <c r="G60" s="2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="H60" s="2"/>
       <c r="I60" s="2"/>
@@ -2876,14 +2858,16 @@
         <v>1059</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>12</v>
+        <v>73</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" s="2"/>
-      <c r="E61" s="2"/>
+      <c r="E61" s="2" t="s">
+        <v>79</v>
+      </c>
       <c r="F61" s="2"/>
       <c r="G61" s="2" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H61" s="2"/>
       <c r="I61" s="2"/>
@@ -2901,16 +2885,16 @@
         <v>1060</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>76</v>
+        <v>12</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" s="2"/>
       <c r="E62" s="2" t="s">
-        <v>82</v>
+        <v>12</v>
       </c>
       <c r="F62" s="2"/>
       <c r="G62" s="2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="H62" s="2"/>
       <c r="I62" s="2"/>
@@ -2932,17 +2916,15 @@
       </c>
       <c r="C63" s="2"/>
       <c r="D63" s="2"/>
-      <c r="E63" s="2" t="s">
-        <v>13</v>
-      </c>
+      <c r="E63" s="2"/>
       <c r="F63" s="2"/>
-      <c r="G63" s="2" t="s">
-        <v>96</v>
-      </c>
+      <c r="G63" s="2"/>
       <c r="H63" s="2"/>
       <c r="I63" s="2"/>
       <c r="J63" s="2"/>
-      <c r="K63" s="2"/>
+      <c r="K63" s="2" t="s">
+        <v>94</v>
+      </c>
       <c r="L63" s="2"/>
       <c r="M63" s="2"/>
       <c r="N63" s="2"/>
@@ -2951,25 +2933,190 @@
       <c r="Q63" s="2"/>
     </row>
     <row r="64" spans="1:17">
-      <c r="A64" s="2"/>
-      <c r="B64" s="2"/>
-      <c r="C64" s="2"/>
-      <c r="D64" s="2"/>
-      <c r="E64" s="2"/>
-      <c r="F64" s="2"/>
-      <c r="G64" s="2"/>
-      <c r="H64" s="2"/>
-      <c r="I64" s="2"/>
-      <c r="J64" s="2"/>
-      <c r="K64" s="2"/>
-      <c r="L64" s="2" t="s">
-        <v>97</v>
-      </c>
+      <c r="A64" s="2">
+        <v>1062</v>
+      </c>
+      <c r="L64" s="2"/>
       <c r="M64" s="2"/>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
       <c r="P64" s="2"/>
       <c r="Q64" s="2"/>
+    </row>
+    <row r="65" spans="1:12">
+      <c r="A65" s="2">
+        <v>1063</v>
+      </c>
+      <c r="L65" s="2"/>
+    </row>
+    <row r="66" spans="1:12">
+      <c r="A66" s="2">
+        <v>1064</v>
+      </c>
+      <c r="L66" s="2"/>
+    </row>
+    <row r="67" spans="1:12">
+      <c r="A67" s="2">
+        <v>1065</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12">
+      <c r="A68" s="2">
+        <v>1066</v>
+      </c>
+    </row>
+    <row r="69" spans="1:12">
+      <c r="A69" s="2">
+        <v>1067</v>
+      </c>
+    </row>
+    <row r="70" spans="1:12">
+      <c r="A70" s="2">
+        <v>1068</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12">
+      <c r="A71" s="2">
+        <v>1069</v>
+      </c>
+    </row>
+    <row r="72" spans="1:12">
+      <c r="A72" s="2">
+        <v>1070</v>
+      </c>
+    </row>
+    <row r="73" spans="1:12">
+      <c r="A73" s="2">
+        <v>1071</v>
+      </c>
+    </row>
+    <row r="74" spans="1:12">
+      <c r="A74" s="2">
+        <v>1072</v>
+      </c>
+    </row>
+    <row r="75" spans="1:12">
+      <c r="A75" s="2">
+        <v>1073</v>
+      </c>
+    </row>
+    <row r="76" ht="112" spans="1:12">
+      <c r="A76" s="2">
+        <v>1074</v>
+      </c>
+      <c r="H76" s="4" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="77" spans="1:12">
+      <c r="A77" s="2">
+        <v>1075</v>
+      </c>
+      <c r="H77" s="2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12">
+      <c r="A78" s="2">
+        <v>1076</v>
+      </c>
+      <c r="H78" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="79" spans="1:12">
+      <c r="A79" s="2">
+        <v>1077</v>
+      </c>
+      <c r="H79" s="2" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="80" spans="1:12">
+      <c r="A80" s="2">
+        <v>1078</v>
+      </c>
+      <c r="H80" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8">
+      <c r="A81" s="2">
+        <v>1079</v>
+      </c>
+      <c r="H81" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8">
+      <c r="A82" s="2">
+        <v>1080</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8">
+      <c r="A83" s="2">
+        <v>1081</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8">
+      <c r="A84" s="2">
+        <v>1082</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8">
+      <c r="A85" s="2">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8">
+      <c r="A86" s="2">
+        <v>1084</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8">
+      <c r="A87" s="2">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8">
+      <c r="A88" s="2">
+        <v>1086</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8">
+      <c r="A89" s="2">
+        <v>1087</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8">
+      <c r="A90" s="2">
+        <v>1088</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8">
+      <c r="A91" s="2">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8">
+      <c r="A92" s="2">
+        <v>1090</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8">
+      <c r="A93" s="2">
+        <v>1091</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8">
+      <c r="A94" s="2">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8">
+      <c r="A95" s="2">
+        <v>1093</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/gal/Assets/Resources/VNovelizerRes/ExcelVNScripts/第三章.xlsx
+++ b/gal/Assets/Resources/VNovelizerRes/ExcelVNScripts/第三章.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="102">
   <si>
     <t>ID</t>
   </si>
@@ -95,7 +95,7 @@
     <t>害，如果能一直带薪休假就好了</t>
   </si>
   <si>
-    <t>我是不是好久都没看手机消息了</t>
+    <t>不过我是不是好久都没看手机消息了</t>
   </si>
   <si>
     <t>打开手机看一眼吧</t>
@@ -104,19 +104,22 @@
     <t>同事</t>
   </si>
   <si>
-    <t>"你身体咋样了"</t>
-  </si>
-  <si>
-    <t>"好好休息"</t>
-  </si>
-  <si>
-    <t>"？还活着吗"</t>
+    <t>“你身体咋样了”</t>
+  </si>
+  <si>
+    <t>病房2</t>
+  </si>
+  <si>
+    <t>“好好休息”</t>
+  </si>
+  <si>
+    <t>“？还活着吗”</t>
   </si>
   <si>
     <t>我靠，两天没回他消息了</t>
   </si>
   <si>
-    <t>"还活着，恢复得比想象中快，应该过几天就出院了"</t>
+    <t>“还活着，恢复得比想象中快，应该过几天就出院了”</t>
   </si>
   <si>
     <t>放下手机</t>
@@ -1556,7 +1559,9 @@
       <c r="G10" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="H10" s="2"/>
+      <c r="H10" s="2" t="s">
+        <v>26</v>
+      </c>
       <c r="I10" s="2"/>
       <c r="J10" s="2"/>
       <c r="K10" s="2"/>
@@ -1579,7 +1584,7 @@
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
       <c r="G11" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H11" s="2"/>
       <c r="I11" s="2"/>
@@ -1604,7 +1609,7 @@
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
       <c r="G12" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
@@ -1629,7 +1634,7 @@
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
       <c r="G13" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H13" s="2"/>
       <c r="I13" s="2"/>
@@ -1654,7 +1659,7 @@
       <c r="E14" s="2"/>
       <c r="F14" s="2"/>
       <c r="G14" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H14" s="2"/>
       <c r="I14" s="2"/>
@@ -1679,9 +1684,11 @@
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
       <c r="G15" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="H15" s="2"/>
+        <v>31</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>14</v>
+      </c>
       <c r="I15" s="2"/>
       <c r="J15" s="2"/>
       <c r="K15" s="2"/>
@@ -1704,9 +1711,11 @@
       <c r="E16" s="2"/>
       <c r="F16" s="2"/>
       <c r="G16" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="H16" s="2"/>
+        <v>32</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>26</v>
+      </c>
       <c r="I16" s="2"/>
       <c r="J16" s="2"/>
       <c r="K16" s="2"/>
@@ -1725,7 +1734,7 @@
         <v>12</v>
       </c>
       <c r="G17" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M17" s="2"/>
       <c r="N17" s="2"/>
@@ -1745,7 +1754,7 @@
       <c r="E18" s="2"/>
       <c r="F18" s="2"/>
       <c r="G18" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
@@ -1763,14 +1772,14 @@
         <v>1017</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" s="2"/>
       <c r="E19" s="2"/>
       <c r="F19" s="2"/>
       <c r="G19" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H19" s="2"/>
       <c r="I19" s="2"/>
@@ -1788,14 +1797,14 @@
         <v>1018</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
       <c r="E20" s="2"/>
       <c r="F20" s="2"/>
       <c r="G20" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H20" s="2"/>
       <c r="I20" s="2"/>
@@ -1820,7 +1829,7 @@
       <c r="E21" s="2"/>
       <c r="F21" s="2"/>
       <c r="G21" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H21" s="2"/>
       <c r="I21" s="2"/>
@@ -1838,14 +1847,14 @@
         <v>1020</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
       <c r="E22" s="2"/>
       <c r="F22" s="2"/>
       <c r="G22" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H22" s="2"/>
       <c r="I22" s="2"/>
@@ -1870,7 +1879,7 @@
       <c r="E23" s="2"/>
       <c r="F23" s="2"/>
       <c r="G23" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H23" s="2"/>
       <c r="I23" s="2"/>
@@ -1895,9 +1904,11 @@
       <c r="E24" s="2"/>
       <c r="F24" s="2"/>
       <c r="G24" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="H24" s="2"/>
+        <v>41</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>14</v>
+      </c>
       <c r="I24" s="2"/>
       <c r="J24" s="2"/>
       <c r="K24" s="2"/>
@@ -1920,7 +1931,7 @@
       <c r="E25" s="2"/>
       <c r="F25" s="2"/>
       <c r="G25" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H25" s="2"/>
       <c r="I25" s="2"/>
@@ -1945,7 +1956,7 @@
       <c r="E26" s="2"/>
       <c r="F26" s="2"/>
       <c r="G26" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H26" s="2"/>
       <c r="I26" s="2"/>
@@ -1970,7 +1981,7 @@
       <c r="E27" s="2"/>
       <c r="F27" s="2"/>
       <c r="G27" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H27" s="2"/>
       <c r="I27" s="2"/>
@@ -1988,14 +1999,14 @@
         <v>1026</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" s="2"/>
       <c r="E28" s="2"/>
       <c r="F28" s="2"/>
       <c r="G28" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H28" s="2"/>
       <c r="I28" s="2"/>
@@ -2013,14 +2024,14 @@
         <v>1027</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" s="2"/>
       <c r="E29" s="2"/>
       <c r="F29" s="2"/>
       <c r="G29" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H29" s="2"/>
       <c r="I29" s="2"/>
@@ -2038,14 +2049,14 @@
         <v>1028</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" s="2"/>
       <c r="E30" s="2"/>
       <c r="F30" s="2"/>
       <c r="G30" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H30" s="2"/>
       <c r="I30" s="2"/>
@@ -2063,14 +2074,14 @@
         <v>1029</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" s="2"/>
       <c r="E31" s="2"/>
       <c r="F31" s="2"/>
       <c r="G31" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H31" s="2"/>
       <c r="I31" s="2"/>
@@ -2088,14 +2099,14 @@
         <v>1030</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" s="2"/>
       <c r="E32" s="2"/>
       <c r="F32" s="2"/>
       <c r="G32" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H32" s="2"/>
       <c r="I32" s="2"/>
@@ -2113,14 +2124,14 @@
         <v>1031</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" s="2"/>
       <c r="E33" s="2"/>
       <c r="F33" s="2"/>
       <c r="G33" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H33" s="2"/>
       <c r="I33" s="2"/>
@@ -2138,14 +2149,14 @@
         <v>1032</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" s="2"/>
       <c r="E34" s="2"/>
       <c r="F34" s="2"/>
       <c r="G34" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H34" s="2"/>
       <c r="I34" s="2"/>
@@ -2154,10 +2165,10 @@
       <c r="L34" s="2"/>
       <c r="M34" s="2"/>
       <c r="N34" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="O34" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="P34" s="2"/>
       <c r="Q34" s="2"/>
@@ -2174,7 +2185,7 @@
       <c r="E35" s="2"/>
       <c r="F35" s="2"/>
       <c r="G35" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H35" s="2"/>
       <c r="I35" s="2"/>
@@ -2182,7 +2193,7 @@
       <c r="K35" s="2"/>
       <c r="L35" s="2"/>
       <c r="M35" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="N35" s="3"/>
       <c r="O35" s="3"/>
@@ -2194,14 +2205,14 @@
         <v>1034</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" s="2"/>
       <c r="E36" s="2"/>
       <c r="F36" s="2"/>
       <c r="G36" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H36" s="2"/>
       <c r="I36" s="2"/>
@@ -2209,7 +2220,7 @@
       <c r="K36" s="2"/>
       <c r="L36" s="2"/>
       <c r="M36" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -2221,14 +2232,14 @@
         <v>1035</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" s="2"/>
       <c r="E37" s="2"/>
       <c r="F37" s="2"/>
       <c r="G37" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H37" s="2"/>
       <c r="I37" s="2"/>
@@ -2236,7 +2247,7 @@
       <c r="K37" s="2"/>
       <c r="L37" s="2"/>
       <c r="M37" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -2248,14 +2259,14 @@
         <v>1036</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" s="2"/>
       <c r="E38" s="2"/>
       <c r="F38" s="2"/>
       <c r="G38" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H38" s="2"/>
       <c r="I38" s="2"/>
@@ -2263,7 +2274,7 @@
       <c r="K38" s="2"/>
       <c r="L38" s="2"/>
       <c r="M38" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -2282,7 +2293,7 @@
       <c r="E39" s="2"/>
       <c r="F39" s="2"/>
       <c r="G39" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H39" s="2"/>
       <c r="I39" s="2"/>
@@ -2290,11 +2301,11 @@
       <c r="K39" s="2"/>
       <c r="L39" s="2"/>
       <c r="M39" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="P39" s="2"/>
       <c r="Q39" s="2"/>
@@ -2304,14 +2315,14 @@
         <v>1038</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" s="2"/>
       <c r="E40" s="2"/>
       <c r="F40" s="2"/>
       <c r="G40" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H40" s="2"/>
       <c r="I40" s="2"/>
@@ -2319,7 +2330,7 @@
       <c r="K40" s="2"/>
       <c r="L40" s="2"/>
       <c r="M40" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -2331,14 +2342,14 @@
         <v>1039</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" s="2"/>
       <c r="E41" s="2"/>
       <c r="F41" s="2"/>
       <c r="G41" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H41" s="2"/>
       <c r="I41" s="2"/>
@@ -2346,11 +2357,11 @@
       <c r="K41" s="2"/>
       <c r="L41" s="2"/>
       <c r="M41" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="P41" s="3"/>
       <c r="Q41" s="3"/>
@@ -2367,17 +2378,17 @@
       <c r="E42" s="2"/>
       <c r="F42" s="2"/>
       <c r="G42" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I42" s="2"/>
       <c r="J42" s="2"/>
       <c r="K42" s="2"/>
       <c r="L42" s="2"/>
       <c r="M42" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -2396,7 +2407,7 @@
       <c r="E43" s="2"/>
       <c r="F43" s="2"/>
       <c r="G43" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H43" s="2"/>
       <c r="I43" s="2"/>
@@ -2413,12 +2424,24 @@
       <c r="A44" s="2">
         <v>1042</v>
       </c>
-      <c r="B44" t="s">
-        <v>12</v>
+      <c r="B44" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C44" s="2"/>
+      <c r="D44" s="2"/>
+      <c r="E44" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="F44" s="2"/>
+      <c r="G44" s="2" t="s">
+        <v>76</v>
       </c>
       <c r="H44" s="2" t="s">
         <v>14</v>
       </c>
+      <c r="I44" s="2"/>
+      <c r="J44" s="2"/>
+      <c r="K44" s="2"/>
       <c r="M44" s="2"/>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -2430,16 +2453,16 @@
         <v>1043</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>73</v>
+        <v>35</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" s="2"/>
       <c r="E45" s="2" t="s">
-        <v>74</v>
+        <v>12</v>
       </c>
       <c r="F45" s="2"/>
       <c r="G45" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H45" s="2"/>
       <c r="I45" s="2"/>
@@ -2457,16 +2480,16 @@
         <v>1044</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>34</v>
+        <v>74</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" s="2"/>
       <c r="E46" s="2" t="s">
-        <v>12</v>
+        <v>78</v>
       </c>
       <c r="F46" s="2"/>
       <c r="G46" s="2" t="s">
-        <v>76</v>
+        <v>41</v>
       </c>
       <c r="H46" s="2"/>
       <c r="I46" s="2"/>
@@ -2484,16 +2507,16 @@
         <v>1045</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>73</v>
+        <v>35</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" s="2"/>
       <c r="E47" s="2" t="s">
-        <v>77</v>
+        <v>12</v>
       </c>
       <c r="F47" s="2"/>
       <c r="G47" s="2" t="s">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="H47" s="2"/>
       <c r="I47" s="2"/>
@@ -2511,16 +2534,16 @@
         <v>1046</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>34</v>
+        <v>74</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" s="2"/>
       <c r="E48" s="2" t="s">
-        <v>12</v>
+        <v>80</v>
       </c>
       <c r="F48" s="2"/>
       <c r="G48" s="2" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="H48" s="2"/>
       <c r="I48" s="2"/>
@@ -2538,16 +2561,16 @@
         <v>1047</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>73</v>
+        <v>35</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" s="2"/>
       <c r="E49" s="2" t="s">
-        <v>79</v>
+        <v>12</v>
       </c>
       <c r="F49" s="2"/>
       <c r="G49" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H49" s="2"/>
       <c r="I49" s="2"/>
@@ -2565,16 +2588,16 @@
         <v>1048</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>34</v>
+        <v>74</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" s="2"/>
       <c r="E50" s="2" t="s">
-        <v>12</v>
+        <v>75</v>
       </c>
       <c r="F50" s="2"/>
       <c r="G50" s="2" t="s">
-        <v>81</v>
+        <v>41</v>
       </c>
       <c r="H50" s="2"/>
       <c r="I50" s="2"/>
@@ -2592,16 +2615,16 @@
         <v>1049</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>73</v>
+        <v>35</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" s="2"/>
       <c r="E51" s="2" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="F51" s="2"/>
       <c r="G51" s="2" t="s">
-        <v>40</v>
+        <v>84</v>
       </c>
       <c r="H51" s="2"/>
       <c r="I51" s="2"/>
@@ -2619,16 +2642,16 @@
         <v>1050</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>34</v>
+        <v>74</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" s="2"/>
       <c r="E52" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F52" s="2"/>
       <c r="G52" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="H52" s="2"/>
       <c r="I52" s="2"/>
@@ -2646,16 +2669,14 @@
         <v>1051</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>73</v>
+        <v>35</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" s="2"/>
-      <c r="E53" s="2" t="s">
-        <v>82</v>
-      </c>
+      <c r="E53" s="2"/>
       <c r="F53" s="2"/>
       <c r="G53" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H53" s="2"/>
       <c r="I53" s="2"/>
@@ -2673,14 +2694,16 @@
         <v>1052</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>34</v>
+        <v>74</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" s="2"/>
-      <c r="E54" s="2"/>
+      <c r="E54" s="2" t="s">
+        <v>78</v>
+      </c>
       <c r="F54" s="2"/>
       <c r="G54" s="2" t="s">
-        <v>85</v>
+        <v>41</v>
       </c>
       <c r="H54" s="2"/>
       <c r="I54" s="2"/>
@@ -2698,16 +2721,16 @@
         <v>1053</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" s="2"/>
       <c r="E55" s="2" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="F55" s="2"/>
       <c r="G55" s="2" t="s">
-        <v>40</v>
+        <v>88</v>
       </c>
       <c r="H55" s="2"/>
       <c r="I55" s="2"/>
@@ -2725,16 +2748,16 @@
         <v>1054</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>73</v>
+        <v>35</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" s="2"/>
       <c r="E56" s="2" t="s">
-        <v>86</v>
+        <v>12</v>
       </c>
       <c r="F56" s="2"/>
       <c r="G56" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="H56" s="2"/>
       <c r="I56" s="2"/>
@@ -2752,16 +2775,16 @@
         <v>1055</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>34</v>
+        <v>74</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" s="2"/>
       <c r="E57" s="2" t="s">
-        <v>12</v>
+        <v>80</v>
       </c>
       <c r="F57" s="2"/>
       <c r="G57" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H57" s="2"/>
       <c r="I57" s="2"/>
@@ -2779,16 +2802,16 @@
         <v>1056</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>73</v>
+        <v>12</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" s="2"/>
       <c r="E58" s="2" t="s">
-        <v>79</v>
+        <v>12</v>
       </c>
       <c r="F58" s="2"/>
       <c r="G58" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H58" s="2"/>
       <c r="I58" s="2"/>
@@ -2806,16 +2829,14 @@
         <v>1057</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" s="2"/>
-      <c r="E59" s="2" t="s">
-        <v>12</v>
-      </c>
+      <c r="E59" s="2"/>
       <c r="F59" s="2"/>
       <c r="G59" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H59" s="2"/>
       <c r="I59" s="2"/>
@@ -2833,14 +2854,16 @@
         <v>1058</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>34</v>
+        <v>74</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" s="2"/>
-      <c r="E60" s="2"/>
+      <c r="E60" s="2" t="s">
+        <v>80</v>
+      </c>
       <c r="F60" s="2"/>
       <c r="G60" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="H60" s="2"/>
       <c r="I60" s="2"/>
@@ -2858,16 +2881,16 @@
         <v>1059</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>73</v>
+        <v>12</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" s="2"/>
       <c r="E61" s="2" t="s">
-        <v>79</v>
+        <v>12</v>
       </c>
       <c r="F61" s="2"/>
       <c r="G61" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H61" s="2"/>
       <c r="I61" s="2"/>
@@ -2889,17 +2912,15 @@
       </c>
       <c r="C62" s="2"/>
       <c r="D62" s="2"/>
-      <c r="E62" s="2" t="s">
-        <v>12</v>
-      </c>
+      <c r="E62" s="2"/>
       <c r="F62" s="2"/>
-      <c r="G62" s="2" t="s">
-        <v>93</v>
-      </c>
+      <c r="G62" s="2"/>
       <c r="H62" s="2"/>
       <c r="I62" s="2"/>
       <c r="J62" s="2"/>
-      <c r="K62" s="2"/>
+      <c r="K62" s="2" t="s">
+        <v>95</v>
+      </c>
       <c r="L62" s="2"/>
       <c r="M62" s="2"/>
       <c r="N62" s="2"/>
@@ -2911,20 +2932,6 @@
       <c r="A63" s="2">
         <v>1061</v>
       </c>
-      <c r="B63" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C63" s="2"/>
-      <c r="D63" s="2"/>
-      <c r="E63" s="2"/>
-      <c r="F63" s="2"/>
-      <c r="G63" s="2"/>
-      <c r="H63" s="2"/>
-      <c r="I63" s="2"/>
-      <c r="J63" s="2"/>
-      <c r="K63" s="2" t="s">
-        <v>94</v>
-      </c>
       <c r="L63" s="2"/>
       <c r="M63" s="2"/>
       <c r="N63" s="2"/>
@@ -3005,7 +3012,7 @@
         <v>1074</v>
       </c>
       <c r="H76" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="77" spans="1:12">
@@ -3013,7 +3020,7 @@
         <v>1075</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="78" spans="1:12">
@@ -3021,7 +3028,7 @@
         <v>1076</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="79" spans="1:12">
@@ -3029,7 +3036,7 @@
         <v>1077</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="80" spans="1:12">
@@ -3037,7 +3044,7 @@
         <v>1078</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="81" spans="1:8">
@@ -3045,7 +3052,7 @@
         <v>1079</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="82" spans="1:8">
